--- a/backend python/Tema04 - Base de datos/Clase10_09-30-2026/03.CursosBD.xlsx
+++ b/backend python/Tema04 - Base de datos/Clase10_09-30-2026/03.CursosBD.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jhonathan\Documentos\Cursos\CODIGO\Python Online G30\Sesiones\Tema04 - Base de datos\Clase10_09-30-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/49ff2d670b27dd99/AAA PC JYG OneDrive/Documentos JYG/Cursos JYG/WebFullstackPythonAI tecsup2025/1 frontend foundation webfullstack/backend python/Tema04 - Base de datos/Clase10_09-30-2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E2F8F63-0CA1-4904-AB9E-2CD3C9319E5C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{4E2F8F63-0CA1-4904-AB9E-2CD3C9319E5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0155D085-1932-404F-8CE4-209E6B27A5BF}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="18760" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="categorias" sheetId="1" r:id="rId1"/>
-    <sheet name="instructores" sheetId="2" r:id="rId2"/>
-    <sheet name="horarios" sheetId="3" r:id="rId3"/>
-    <sheet name="cursos" sheetId="4" r:id="rId4"/>
+    <sheet name="cursos" sheetId="4" r:id="rId1"/>
+    <sheet name="categorias" sheetId="1" r:id="rId2"/>
+    <sheet name="instructores" sheetId="2" r:id="rId3"/>
+    <sheet name="horarios" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -507,14 +507,323 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2D76170-8CDC-44CE-A6A8-3CADF8F54A2E}">
+  <dimension ref="A1:J12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="3.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2">
+        <v>800</v>
+      </c>
+      <c r="G2">
+        <v>24</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>12</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3">
+        <v>1200</v>
+      </c>
+      <c r="G3">
+        <v>24</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4">
+        <v>1600</v>
+      </c>
+      <c r="G4">
+        <v>36</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5">
+        <v>1600</v>
+      </c>
+      <c r="G5">
+        <v>36</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6">
+        <v>500</v>
+      </c>
+      <c r="G6">
+        <v>24</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7">
+        <v>500</v>
+      </c>
+      <c r="G7">
+        <v>24</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8">
+        <v>600</v>
+      </c>
+      <c r="G8">
+        <v>24</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8">
+        <v>3</v>
+      </c>
+      <c r="J8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9">
+        <v>1200</v>
+      </c>
+      <c r="G9">
+        <v>48</v>
+      </c>
+      <c r="H9">
+        <v>2</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10">
+        <v>1200</v>
+      </c>
+      <c r="G10">
+        <v>48</v>
+      </c>
+      <c r="H10">
+        <v>2</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11">
+        <v>1200</v>
+      </c>
+      <c r="G11">
+        <v>48</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11">
+        <v>3</v>
+      </c>
+      <c r="J11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12">
+        <v>800</v>
+      </c>
+      <c r="G12">
+        <v>24</v>
+      </c>
+      <c r="H12">
+        <v>4</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -522,7 +831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -530,7 +839,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -538,7 +847,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -546,7 +855,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -560,15 +869,15 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42CAD8C9-0D34-463A-87D8-FCE19B8C623C}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="11.5703125" customWidth="1"/>
+    <col min="2" max="2" width="11.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -591,7 +900,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -602,7 +911,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -613,7 +922,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -622,75 +931,6 @@
       </c>
       <c r="C4" t="s">
         <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36E42368-3897-47E0-9690-45F2B60089F8}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -699,307 +939,67 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2D76170-8CDC-44CE-A6A8-3CADF8F54A2E}">
-  <dimension ref="A1:J12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36E42368-3897-47E0-9690-45F2B60089F8}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2">
-        <v>800</v>
-      </c>
-      <c r="G2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
         <v>24</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>12</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3">
-        <v>1200</v>
-      </c>
-      <c r="G3">
-        <v>24</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>13</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
       <c r="C4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4">
-        <v>1600</v>
-      </c>
-      <c r="G4">
-        <v>36</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
       <c r="C5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5">
-        <v>1600</v>
-      </c>
-      <c r="G5">
-        <v>36</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6">
-        <v>500</v>
-      </c>
-      <c r="G6">
-        <v>24</v>
-      </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7">
-        <v>500</v>
-      </c>
-      <c r="G7">
-        <v>24</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F8">
-        <v>600</v>
-      </c>
-      <c r="G8">
-        <v>24</v>
-      </c>
-      <c r="H8">
-        <v>3</v>
-      </c>
-      <c r="I8">
-        <v>3</v>
-      </c>
-      <c r="J8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9">
-        <v>1200</v>
-      </c>
-      <c r="G9">
-        <v>48</v>
-      </c>
-      <c r="H9">
-        <v>2</v>
-      </c>
-      <c r="I9">
-        <v>2</v>
-      </c>
-      <c r="J9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="C10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10">
-        <v>1200</v>
-      </c>
-      <c r="G10">
-        <v>48</v>
-      </c>
-      <c r="H10">
-        <v>2</v>
-      </c>
-      <c r="I10">
-        <v>1</v>
-      </c>
-      <c r="J10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="C11" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11">
-        <v>1200</v>
-      </c>
-      <c r="G11">
-        <v>48</v>
-      </c>
-      <c r="H11">
-        <v>2</v>
-      </c>
-      <c r="I11">
-        <v>3</v>
-      </c>
-      <c r="J11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="C12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F12">
-        <v>800</v>
-      </c>
-      <c r="G12">
-        <v>24</v>
-      </c>
-      <c r="H12">
-        <v>4</v>
-      </c>
-      <c r="I12">
-        <v>1</v>
-      </c>
-      <c r="J12">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
